--- a/data/sources/countries/venezuela.xlsx
+++ b/data/sources/countries/venezuela.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI80"/>
+  <dimension ref="A1:BE83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -827,7 +731,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -865,12 +769,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Construcción en la instalación del sistema VEN911</t>
+          <t>Construcción En La Instalación Del Sistema Ven911</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Construction to install VEN911 system</t>
+          <t>Construction To Install Ven911 System</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -895,17 +799,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>Sistema SIMA-VEN911 de CEIEC. Confirmado por el Departamento del Tesoro de EEUU, que sanciono a la empresa en 2020, el informe de Transparencia Venezuela, Global Voices, TalCual e Infobae. ATENCION AL MONTO: el anuncio de 2013 fue de USD 1.200M, no 1.000, para 40 centros de mando en 16 localidades y 30.000 camaras, y Transparencia Venezuela estima sobreprecio de hasta USD 350M. Es monto anunciado, no ejecutado verificado.</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -935,7 +828,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -987,7 +880,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1003,17 +896,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1043,7 +925,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -1095,7 +977,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1111,17 +993,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1151,7 +1022,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -1203,7 +1074,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1219,17 +1090,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1259,7 +1119,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -1311,7 +1171,7 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1327,17 +1187,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1367,7 +1216,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -1419,7 +1268,7 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1435,17 +1284,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1475,7 +1313,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -1527,7 +1365,7 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1543,17 +1381,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1583,7 +1410,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -1635,7 +1462,7 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1651,17 +1478,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1691,7 +1507,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -1743,7 +1559,7 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1759,17 +1575,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1799,7 +1604,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -1851,7 +1656,7 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1867,17 +1672,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1907,7 +1701,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -1959,7 +1753,7 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1975,17 +1769,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2015,7 +1798,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -2067,7 +1850,7 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2083,17 +1866,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2123,7 +1895,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -2175,7 +1947,7 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2191,17 +1963,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2231,7 +1992,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -2283,7 +2044,7 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2299,17 +2060,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2339,7 +2089,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -2391,7 +2141,7 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2407,17 +2157,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2447,7 +2186,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -2499,7 +2238,7 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2515,17 +2254,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2555,7 +2283,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -2607,7 +2335,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2623,17 +2351,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2663,7 +2380,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -2715,7 +2432,7 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2731,17 +2448,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2771,7 +2477,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -2823,7 +2529,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2839,17 +2545,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2879,7 +2574,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -2931,7 +2626,7 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2947,17 +2642,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2987,7 +2671,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -3039,7 +2723,7 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3055,17 +2739,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -3095,7 +2768,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -3147,7 +2820,7 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3163,17 +2836,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3203,7 +2865,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -3255,7 +2917,7 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3271,17 +2933,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC24" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3311,7 +2962,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -3363,7 +3014,7 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -3379,17 +3030,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA25" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3419,7 +3059,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -3471,7 +3111,7 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -3487,17 +3127,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB26" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3527,7 +3156,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -3579,7 +3208,7 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -3595,17 +3224,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA27" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB27" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3635,7 +3253,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -3687,7 +3305,7 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -3703,17 +3321,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3743,7 +3350,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -3795,7 +3402,7 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3811,17 +3418,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA29" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB29" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3851,7 +3447,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -3903,7 +3499,7 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3919,17 +3515,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB30" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3959,7 +3544,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -4011,7 +3596,7 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4027,17 +3612,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB31" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4067,7 +3641,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -4119,7 +3693,7 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -4135,17 +3709,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4175,7 +3738,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -4227,7 +3790,7 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -4243,17 +3806,6 @@
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="BA33" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
-        </is>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4283,7 +3835,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -4321,12 +3873,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Construcción en mejoración de la refinería de crudo Puerto La Cruz</t>
+          <t>Construcción En Mejoración De La Refinería De Crudo Puerto La Cruz</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Construction on upgrade to Puerto La Cruz oil refinery</t>
+          <t>Construction On Upgrade To Puerto La Cruz Oil Refinery</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4355,25 +3907,17 @@
       <c r="BA34" t="n">
         <v>4</v>
       </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>Confirmado: Wison Engineering (junto a Hyundai) ganó contrato EPC para mejora de la refinería Puerto La Cruz (PDVSA), con contrato total de \~USD 2.993B anunciado en 2012. La porción de Wison fue \~USD 927M. El monto registrado USD 550M podría ser un contrato parcial o la fase de preparación del sitio. Wison.com, PR Newswire y AidData confirman el proyecto. Discrepancia en monto: la entrada (USD 550M) podría corresponder a un subcontrato específico.</t>
-        </is>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>https://www.wison.com/en/read_page/819</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/wison-wins-puerto-la-cruz-oil-refinery-in-venezuela-160517955.html</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
-        <is>
-          <t>https://www.wison.com/en/read_page/819</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>https://www.prnewswire.com/news-releases/wison-wins-puerto-la-cruz-oil-refinery-in-venezuela-160517955.html</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/58367/</t>
         </is>
@@ -4406,7 +3950,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -4444,12 +3988,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Proyecto de viviendas Ciudad Tiuna</t>
+          <t>Proyecto De Viviendas Ciudad Tiuna</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ciudad Tiuna housing project</t>
+          <t>Ciudad Tiuna Housing Project</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4478,25 +4022,17 @@
       <c r="BA35" t="n">
         <v>4</v>
       </c>
-      <c r="BB35" t="inlineStr">
-        <is>
-          <t>Confirmado: CITIC Construction fue contratada para el proyecto habitacional en Ciudad Tiuna (Fuerte Tiuna, Caracas), construyendo 13.034 apartamentos en 116 edificios. El sitio oficial de CITIC Construction, People's Daily y la ceremonia de entrega presidencial confirman el proyecto. El monto USD 1.190M no aparece explícitamente en las fuentes encontradas pero es coherente con la magnitud del proyecto (13.034 unidades).</t>
-        </is>
-      </c>
-      <c r="BC35" t="n">
-        <v>0</v>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>https://www.construction.citic/en/global/project/lad/2660</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>https://en.people.cn/n/2015/0505/c90883-8887435.html</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
-        <is>
-          <t>https://www.construction.citic/en/global/project/lad/2660</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>https://en.people.cn/n/2015/0505/c90883-8887435.html</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr">
         <is>
           <t>https://www.construction.citic/en/news/latest/2432</t>
         </is>
@@ -4529,7 +4065,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -4567,12 +4103,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Adquisicion de participación en Corpivensa para crear Vtelca</t>
+          <t>Adquisicion De Participación En Corpivensa Para Crear Vtelca</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Acquisition of stake in Corpivensa to create Vtelca</t>
+          <t>Acquisition Of Stake In Corpivensa To Create Vtelca</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4601,25 +4137,17 @@
       <c r="BA36" t="n">
         <v>4</v>
       </c>
-      <c r="BB36" t="inlineStr">
-        <is>
-          <t>Confirmado: ZTE y CORPIVENSA crearon Vtelca (empresa mixta, ZTE 15.7%, CORPIVENSA 84.3%) en Punto Fijo, Falcón, inaugurada en febrero 2009. AidData registra el proyecto con USD 19.5M. Wikipedia en español y Orinoco Tribune confirman la empresa y su historia. El monto USD 10M en la base de datos es inferior a los USD 19.5M de AidData; posible diferencia entre aportación de ZTE y costo total.</t>
-        </is>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37442/</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>https://es.wikipedia.org/wiki/Vtelca</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37442/</t>
-        </is>
-      </c>
-      <c r="BF36" t="inlineStr">
-        <is>
-          <t>https://es.wikipedia.org/wiki/Vtelca</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr">
         <is>
           <t>https://orinocotribune.com/president-maduro-celebrates-the-first-10-years-of-vtelca/</t>
         </is>
@@ -4652,7 +4180,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -4690,12 +4218,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Construcción de la termoeléctrica Don Luis Zambrano</t>
+          <t>Construcción De La Termoeléctrica Don Luis Zambrano</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Construction of Don Luis Zambrano thermal plant</t>
+          <t>Construction Of Don Luis Zambrano Thermal Plant</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4724,25 +4252,17 @@
       <c r="BA37" t="n">
         <v>3</v>
       </c>
-      <c r="BB37" t="inlineStr">
-        <is>
-          <t>Confirmado que CAMC Engineering (filial de Sinomach/China Machinery) fue el contratista de la Termoeléctrica Don Luis Zambrano en El Vigía, Mérida (470-570 MW). El inversor registrado es 'China National Machinery Industry Corporation' (Sinomach), que coincide con CAMC. El monto USD 960M es inferior al costo final del proyecto (\~USD 1.045B-1.7B según fuentes, con sobrecostos y corrupción documentada). Score 3 por confirmación del contratista y proyecto con discrepancias de monto y corrupción documentada.</t>
-        </is>
-      </c>
-      <c r="BC37" t="n">
-        <v>0</v>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>https://fundacionandresbello.org/wp-content/uploads/2024/05/perfil-proyecto-termoelectrica-donluiszambrano-pera.pdf</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>http://www.camce.com.cn/sp/enNews/enGN/201505/t20150504_59848.html</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
-        <is>
-          <t>https://fundacionandresbello.org/wp-content/uploads/2024/05/perfil-proyecto-termoelectrica-donluiszambrano-pera.pdf</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>http://www.camce.com.cn/sp/enNews/enGN/201505/t20150504_59848.html</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
         <is>
           <t>https://www.power-technology.com/data-insights/power-plant-profile-don-luis-zambrano-power-plant-venezuela/</t>
         </is>
@@ -4775,7 +4295,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -4813,12 +4333,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Construcción de nuevo terminal de contenedores en Puerto Cabello</t>
+          <t>Construcción De  Nuevo Terminal De Contenedores En Puerto Cabello</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Construction of container terminal in Puerto Cabello</t>
+          <t>Construction Of Container Terminal In Puerto Cabello</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4847,25 +4367,17 @@
       <c r="BA38" t="n">
         <v>5</v>
       </c>
-      <c r="BB38" t="inlineStr">
-        <is>
-          <t>Totalmente confirmado: Bolipuertos y CHEC (China Harbor Engineering, filial de CCCC) firmaron acuerdo en 2011 para construir terminal de contenedores en Puerto Cabello por USD 520M. Offshore Energy, WorldCargo News y Ship Technology confirman todos los detalles (inversor, monto, ubicación). El inversor 'CCCC' en la base de datos es correcto (CHEC es filial).</t>
-        </is>
-      </c>
-      <c r="BC38" t="n">
-        <v>0</v>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>https://www.offshore-energy.biz/venezuela-bolipuertos-chec-agree-to-build-container-terminal-in-puerto-cabello-port/</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>https://www.worldcargonews.com/ports-terminals/2011/10/bolipuertoschec-sign-puerto-cabello-agreement/</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
-        <is>
-          <t>https://www.offshore-energy.biz/venezuela-bolipuertos-chec-agree-to-build-container-terminal-in-puerto-cabello-port/</t>
-        </is>
-      </c>
-      <c r="BF38" t="inlineStr">
-        <is>
-          <t>https://www.worldcargonews.com/ports-terminals/2011/10/bolipuertoschec-sign-puerto-cabello-agreement/</t>
-        </is>
-      </c>
-      <c r="BG38" t="inlineStr">
         <is>
           <t>https://www.ship-technology.com/news/newsbolipuertos-and-chec-to-build-new-terminal-at-puerto-cabello-port-venezuela/</t>
         </is>
@@ -4898,7 +4410,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -4936,12 +4448,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Construcción para la renovación de la represa Guri</t>
+          <t>Construcción Para La Renovación De La Represa Guri</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Construction in renovation of Guri dam</t>
+          <t>Construction In Renovation Of Guri Dam</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4970,30 +4482,17 @@
       <c r="BA39" t="n">
         <v>1</v>
       </c>
-      <c r="BB39" t="inlineStr">
-        <is>
-          <t>Se confirma que Corpoelec adjudicó contrato a Dongfang Electric en octubre 2014 para modernización de 6 turbinas-generadores de la central Simón Bolívar (Guri). Sin embargo, las fuentes principales de la modernización histórica mencionan a ABB y Andritz Hydro como contratistas principales. Allison señala que según CAF y BID, la Corporación Eléctrica Nacional S.A. (venezolana) es la encargada de la construcción. El monto de USD 1,310M parece muy elevado y no se pudo confirmar. El contrato de Dongfang parece ser para suministro de equipos, no construcción completa.</t>
-        </is>
-      </c>
-      <c r="BC39" t="n">
-        <v>1</v>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>https://www.power-technology.com/projects/gurihydroelectric/</t>
+        </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
+          <t>https://en.wikipedia.org/wiki/Guri_Dam</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
-        <is>
-          <t>https://www.power-technology.com/projects/gurihydroelectric/</t>
-        </is>
-      </c>
-      <c r="BF39" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Guri_Dam</t>
-        </is>
-      </c>
-      <c r="BG39" t="inlineStr">
         <is>
           <t>https://www.hydroreview.com/world-regions/venezuela-further-extends-engineering-call-to-upgrade-10-300-mw-simon-bolivar-hydro-project/</t>
         </is>
@@ -5026,7 +4525,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -5064,12 +4563,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Adquisicion de participación en PdVSA para crear Petrozumano</t>
+          <t>Adquisicion De Participación En Pdvsa Para Crear Petrozumano</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Acquisition of stake in PdVSA to create Petrozumano</t>
+          <t>Acquisition Of Stake In Pdvsa To Create Petrozumano</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5095,25 +4594,17 @@
       <c r="BA40" t="n">
         <v>4</v>
       </c>
-      <c r="BB40" t="inlineStr">
-        <is>
-          <t>Confirmado: CNPC y PDVSA firmaron en 2004-2007 el JV Petrozumano para explotar el Campo Zumano (Anzoátegui), CNPC con 40%. AidData, Fundación Andrés Bello y Venezuelanalysis confirman el JV. El monto '200\*' (con asterisco, indicando estimación) es coherente con la participación. El año 2007 corresponde a la formalización del JV mediante decreto presidencial.</t>
-        </is>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/38053/</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>https://fundacionandresbello.org/wp-content/uploads/2024/07/pera-perfil-empresa-cnpc-venezuela.pdf</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/38053/</t>
-        </is>
-      </c>
-      <c r="BF40" t="inlineStr">
-        <is>
-          <t>https://fundacionandresbello.org/wp-content/uploads/2024/07/pera-perfil-empresa-cnpc-venezuela.pdf</t>
-        </is>
-      </c>
-      <c r="BG40" t="inlineStr">
         <is>
           <t>https://venezuelanalysis.com/news/15307/</t>
         </is>
@@ -5146,7 +4637,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -5184,12 +4675,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Adquisicion de participación en PdVSA para crear Petrourica</t>
+          <t>Adquisicion De Participación En Pdvsa Para Crear Petrourica</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Acquisition of stake in PdVSA to create Petrourica</t>
+          <t>Acquisition Of Stake In Pdvsa To Create Petrourica</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -5218,25 +4709,17 @@
       <c r="BA41" t="n">
         <v>4</v>
       </c>
-      <c r="BB41" t="inlineStr">
-        <is>
-          <t>Confirmado: CNPC y PDVSA formaron Petrourica (PDVSA 60%, CNPC 40%), JV creado formalmente en diciembre 2011. AidData, Venezuelanalysis y Enerdata confirman el JV. El monto USD 900M y el año 2010 (registro de la negociación/acuerdo previo a la formalización) son coherentes con la inversión china en el bloque Orinoco. Score 4 por múltiples fuentes con leve discrepancia en la fecha exacta de formalización.</t>
-        </is>
-      </c>
-      <c r="BC41" t="n">
-        <v>0</v>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/38053/</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>https://venezuelanalysis.com/news/15307/</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/38053/</t>
-        </is>
-      </c>
-      <c r="BF41" t="inlineStr">
-        <is>
-          <t>https://venezuelanalysis.com/news/15307/</t>
-        </is>
-      </c>
-      <c r="BG41" t="inlineStr">
         <is>
           <t>https://www.enerdata.net/publications/daily-energy-news/pdvsa-secures-new-us22bn-financing-cnpc-raise-oil-output.html</t>
         </is>
@@ -5269,7 +4752,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -5284,7 +4767,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>China National Machinery Industry Corporation</t>
+          <t>China Great Wall Industry Corporation</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5307,12 +4790,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Construcción en el Sistema de Riego del Río Guárico</t>
+          <t>Construcción En El Sistema De Riego Del Río Guárico</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Contract for the rehabilitation and expansion of the Río Guárico Irrigation System</t>
+          <t>Contract For The Rehabilitation And Expansion Of The Río Guárico Irrigation System</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -5341,25 +4824,12 @@
       <c r="BA42" t="n">
         <v>1</v>
       </c>
-      <c r="BB42" t="inlineStr">
-        <is>
-          <t>ERROR DE ATRIBUCION CORREGIDO (Allison): la rehabilitacion del sistema de riego del Rio Guarico la ejecuto Sinomach, no China Great Wall Industry Corporation, que se especializa en satelites y lanzamientos.</t>
-        </is>
-      </c>
-      <c r="BC42" t="n">
-        <v>1</v>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>https://inventariandochina.wordpress.com/2015/10/22/un-contrato-entre-venezuela-y-la-great-wall-industry-corporation/</t>
+        </is>
       </c>
       <c r="BD42" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE42" t="inlineStr">
-        <is>
-          <t>https://inventariandochina.wordpress.com/2015/10/22/un-contrato-entre-venezuela-y-la-great-wall-industry-corporation/</t>
-        </is>
-      </c>
-      <c r="BF42" t="inlineStr">
         <is>
           <t>https://fundacionandresbello.org/wp-content/uploads/2024/05/perfil-proyecto-riegorioguarico-pera.pdf</t>
         </is>
@@ -5392,7 +4862,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -5430,12 +4900,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Adquisición de participación minoritaria en Petrolera Sinovensa</t>
+          <t>Adquisición De Participación Minoritaria En Petrolera Sinovensa</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Acquisition of minority stake in Petrolera Sinovensa</t>
+          <t>Acquisition Of Minority Stake In Petrolera Sinovensa</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -5464,20 +4934,12 @@
       <c r="BA43" t="n">
         <v>3</v>
       </c>
-      <c r="BB43" t="inlineStr">
-        <is>
-          <t>Confirmado por LatinFinance y AidData. Venezuela cedió 9.9% adicional de Petrolera Sinovensa a CNPC en 2018, elevando participación de CNPC Venezuela BV a 49.9%. Base registra $132M. Contexto: proyecto petrolero Orinoco, financiamiento CDB $4B.</t>
-        </is>
-      </c>
-      <c r="BC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE43" t="inlineStr">
+      <c r="BC43" t="inlineStr">
         <is>
           <t>https://latinfinance.com/daily-brief/2018/09/18/venezuela-cedes-sinovensa-stake-to-cnpc/</t>
         </is>
       </c>
-      <c r="BF43" t="inlineStr">
+      <c r="BD43" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/38053/</t>
         </is>
@@ -5510,7 +4972,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -5548,12 +5010,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Construcción de la planta termoeléctrica La Cabrera</t>
+          <t>Construcción De La Planta Termoeléctrica La Cabrera</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Construction of La Cabrera thermoelectric plant</t>
+          <t>Construction Of La Cabrera Thermoelectric Plant</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -5582,25 +5044,17 @@
       <c r="BA44" t="n">
         <v>4</v>
       </c>
-      <c r="BB44" t="inlineStr">
-        <is>
-          <t>Confirmado: Sinohydro construyó la planta termoeléctrica La Cabrera (José Félix Ribas, 320 MW) en la costa norte del Lago Valencia. BNamericas, Power Technology y Dialogue Earth confirman el proyecto y el contratista. El monto USD 604M coincide con las fuentes. Nota: la planta fue comisionada en abril 2014, no 2010; el año 2010 posiblemente refleja inicio del contrato o construcción.</t>
-        </is>
-      </c>
-      <c r="BC44" t="n">
-        <v>0</v>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/electricpower/venezuela-starts-up-320mw-thermo-plant</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>https://www.power-technology.com/data-insights/power-plant-profile-jose-felix-ribas-la-cabrera-power-plant-venezuela/</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/electricpower/venezuela-starts-up-320mw-thermo-plant</t>
-        </is>
-      </c>
-      <c r="BF44" t="inlineStr">
-        <is>
-          <t>https://www.power-technology.com/data-insights/power-plant-profile-jose-felix-ribas-la-cabrera-power-plant-venezuela/</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr">
         <is>
           <t>https://dialogue.earth/en/energy/32585-chinese-investment-in-venezuelas-grid-fails-to-prevent-blackouts/</t>
         </is>
@@ -5633,7 +5087,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -5671,12 +5125,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Construcción para la modernización de plantas de fundición de aluminio</t>
+          <t xml:space="preserve">Construcción Para La Modernización De Plantas De Fundición De Aluminio </t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Construction in the modernization of aluminum foundry plants</t>
+          <t>Construction In The Modernization Of Aluminum Foundry Plants</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -5705,25 +5159,17 @@
       <c r="BA45" t="n">
         <v>3</v>
       </c>
-      <c r="BB45" t="inlineStr">
-        <is>
-          <t>Confirmado que Chalieco (filial de Aluminum Corp. of China/Chalco) firmó contrato de USD 403M con CVG-Alcasa para modernización de fundiciones en Ciudad Guayana en 2011 (no 2014). El inversor 'Aluminum Corporation of China' coincide con el contratista. S\&amp;P Global Platts, Light Metal Age y Aluminium Insider confirman el proyecto. Discrepancias: año (2011 vs 2014) y monto (USD 403M vs USD 500M). Score 3 por confirmación del proyecto con discrepancias.</t>
-        </is>
-      </c>
-      <c r="BC45" t="n">
-        <v>0</v>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/commodityinsights/es/market-insights/latest-news/metals/110411-venezuelas-cvg-alcasa-signs-403-mil-modernization-deal-with-chalieco</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>https://www.lightmetalage.com/news/industry-news/smelting/the-decline-of-venezuelas-aluminum-industry/</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
-        <is>
-          <t>https://www.spglobal.com/commodityinsights/es/market-insights/latest-news/metals/110411-venezuelas-cvg-alcasa-signs-403-mil-modernization-deal-with-chalieco</t>
-        </is>
-      </c>
-      <c r="BF45" t="inlineStr">
-        <is>
-          <t>https://www.lightmetalage.com/news/industry-news/smelting/the-decline-of-venezuelas-aluminum-industry/</t>
-        </is>
-      </c>
-      <c r="BG45" t="inlineStr">
         <is>
           <t>https://aluminiuminsider.com/can-venezuelas-primary-aluminium-industry-survive/</t>
         </is>
@@ -5756,7 +5202,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -5794,12 +5240,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Construcción en la ampliación del Muelle de Palúa</t>
+          <t>Construcción En La Ampliación Del Muelle De Palúa</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Construction on the expansion of Palua dock</t>
+          <t>Construction On The Expansion Of Palua Dock</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -5828,25 +5274,17 @@
       <c r="BA46" t="n">
         <v>4</v>
       </c>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>Confirmado: AidData registra explícitamente un contrato para expansión del Puerto de Palúa otorgado a una corporación china, y BNamericas confirma la expansión de Ferrominera. The Siasat Daily describe el proyecto con China Railway 10th Group. El monto USD 112M y la fecha 2011 están corroborados (el contrato fue dado por CVG Ferrominera el 5 de septiembre 2011). El muelle fue inaugurado en 2017, cinco años tarde.</t>
-        </is>
-      </c>
-      <c r="BC46" t="n">
-        <v>0</v>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37940/</t>
+        </is>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37940/</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BG46" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -5879,7 +5317,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -5917,12 +5355,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Planta de ensamblaje de buses en joint venture con el gobierno de Venezuela</t>
+          <t>Planta De Ensamblaje De Buses En Joint Venture Con El Gobierno De Venezuela</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bus assembly plant in joint venture with the Venezuelan government</t>
+          <t>Bus Assembly Plant In Joint Venture With The Venezuelan Government</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -5951,25 +5389,17 @@
       <c r="BA47" t="n">
         <v>5</v>
       </c>
-      <c r="BB47" t="inlineStr">
-        <is>
-          <t>Totalmente confirmado: Yutong y el gobierno venezolano inauguraron la planta ensambladora en San Felipe, Yaracuy, el 2 de diciembre de 2015, con inversión de USD 278M. TeleSUR, ChinaBuses.org y el Ministerio de Transporte venezolano confirman todos los detalles (inversor, monto, ubicación, fecha, estructura del JV con 85% gobierno / 15% Yutong).</t>
-        </is>
-      </c>
-      <c r="BC47" t="n">
-        <v>0</v>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>https://www.telesurenglish.net/news/Maduro-Opens-Venzeulas-First-Yutong-Bus-Plant-20151203-0006.html</t>
+        </is>
+      </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>https://www.chinabuses.org/news/2015/0721/article_9024.html</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
-        <is>
-          <t>https://www.telesurenglish.net/news/Maduro-Opens-Venzeulas-First-Yutong-Bus-Plant-20151203-0006.html</t>
-        </is>
-      </c>
-      <c r="BF47" t="inlineStr">
-        <is>
-          <t>https://www.chinabuses.org/news/2015/0721/article_9024.html</t>
-        </is>
-      </c>
-      <c r="BG47" t="inlineStr">
         <is>
           <t>https://www.mppt.gob.ve/2016/planta-de-autobuses-yutong-venezuela-ha-ensamblado-100-autobuses-desde-su-inauguracion-en-diciembre/</t>
         </is>
@@ -6002,7 +5432,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -6040,12 +5470,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Proyectos de productividad en Petrozumano y Petrourica</t>
+          <t>Proyectos De Productividad En Petrozumano Y Petrourica</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Productivity projects in Petrozumano and Petrourica</t>
+          <t>Productivity Projects In Petrozumano And Petrourica</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -6074,25 +5504,17 @@
       <c r="BA48" t="n">
         <v>4</v>
       </c>
-      <c r="BB48" t="inlineStr">
-        <is>
-          <t>Confirmado: en noviembre 2016, PDVSA y CNPC firmaron acuerdo de USD 2.200M para proyectos de productividad en Petrozumano y Petrourica. Venezuelanalysis, Enerdata y AidData confirman el acuerdo. El monto USD 1.650M en la base de datos difiere del total de USD 2.200M; podría ser la porción asignada a Petrozumano+Petrourica específicamente (USD 225M + USD 500M = USD 725M; o incluyendo otros fondos). Fecha 2016 es correcta.</t>
-        </is>
-      </c>
-      <c r="BC48" t="n">
-        <v>0</v>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>https://venezuelanalysis.com/news/12792/</t>
+        </is>
+      </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>https://www.enerdata.net/publications/daily-energy-news/pdvsa-secures-new-us22bn-financing-cnpc-raise-oil-output.html</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
-        <is>
-          <t>https://venezuelanalysis.com/news/12792/</t>
-        </is>
-      </c>
-      <c r="BF48" t="inlineStr">
-        <is>
-          <t>https://www.enerdata.net/publications/daily-energy-news/pdvsa-secures-new-us22bn-financing-cnpc-raise-oil-output.html</t>
-        </is>
-      </c>
-      <c r="BG48" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/58413/</t>
         </is>
@@ -6125,7 +5547,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -6163,12 +5585,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Proyectos de productividad en Petrozumano y Petrourica</t>
+          <t>Proyectos De Productividad En Petrozumano Y Petrourica</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Productivity projects in Petrozumano and Petrourica</t>
+          <t>Productivity Projects In Petrozumano And Petrourica</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -6197,25 +5619,17 @@
       <c r="BA49" t="n">
         <v>4</v>
       </c>
-      <c r="BB49" t="inlineStr">
-        <is>
-          <t>Confirmado: en noviembre 2016, PDVSA y CNPC firmaron acuerdo de USD 2.200M para proyectos de productividad en Petrozumano y Petrourica. Venezuelanalysis, Enerdata y AidData confirman el acuerdo. El monto USD 1.650M en la base de datos difiere del total de USD 2.200M; podría ser la porción asignada a Petrozumano+Petrourica específicamente (USD 225M + USD 500M = USD 725M; o incluyendo otros fondos). Fecha 2016 es correcta.</t>
-        </is>
-      </c>
-      <c r="BC49" t="n">
-        <v>0</v>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>https://venezuelanalysis.com/news/12792/</t>
+        </is>
+      </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>https://www.enerdata.net/publications/daily-energy-news/pdvsa-secures-new-us22bn-financing-cnpc-raise-oil-output.html</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
-        <is>
-          <t>https://venezuelanalysis.com/news/12792/</t>
-        </is>
-      </c>
-      <c r="BF49" t="inlineStr">
-        <is>
-          <t>https://www.enerdata.net/publications/daily-energy-news/pdvsa-secures-new-us22bn-financing-cnpc-raise-oil-output.html</t>
-        </is>
-      </c>
-      <c r="BG49" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/58413/</t>
         </is>
@@ -6224,18 +5638,18 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VEN-0103</t>
+          <t>VEN-0101</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>103101</v>
+        <v>101101</v>
       </c>
       <c r="C50" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.729480, -63.100300</t>
+          <t>9.98501014709472, -71.2734985351562</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6248,18 +5662,18 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>VE-B</t>
+          <t>VE-F</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2008</v>
+        <v>1997</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -6286,21 +5700,18 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Adquisicion de participación en PdVSA para crear Petrolera Sinovensa</t>
+          <t>Adquisicion De Participación En Pdvsa Para Crear Petrolera Sino-Venezolana I Y Ii</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Acquisition of stake in PdVSA to create Petrolera Sinvensa</t>
+          <t>Acquisition Of Stake In Pdvsa To Create Petrolera Sino-Venezolana I And Ii</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>ANZOÁTEGUI</t>
-        </is>
-      </c>
-      <c r="R50" t="n">
-        <v>4015</v>
+          <t>BOLÍVAR</t>
+        </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -6320,45 +5731,37 @@
       <c r="BA50" t="n">
         <v>4</v>
       </c>
-      <c r="BB50" t="inlineStr">
-        <is>
-          <t>Confirmado: Sinovensa (PetroSinovensa) fue constituida como JV entre CVP y CNPC Venezuela B.V. en febrero 2008 (Gaceta Oficial N°38.860), con 60% CVP / 40% CNPC. S\&amp;P Global, AidData y SCMP confirman la existencia y detalles del JV. El monto '2000\*' (estimado) para múltiples campos no es verificable directamente; el JV es bien documentado.</t>
-        </is>
-      </c>
-      <c r="BC50" t="n">
-        <v>0</v>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>https://www.cnpc.com.cn/en/America/CNPC_Latin_America.shtml</t>
+        </is>
+      </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>https://fundacionandresbello.org/wp-content/uploads/2024/07/pera-perfil-empresa-cnpc-venezuela.pdf</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>https://www.spglobal.com/energy/en/news-research/latest-news/crude-oil/091520-venezuela-sinovensa-petromonagas-and-petropiar-jvs-restart-production-pdvsa</t>
-        </is>
-      </c>
-      <c r="BF50" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/38053/</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr">
-        <is>
-          <t>https://www.scmp.com/economy/global-economy/article/3338807/what-assets-does-china-have-venezuela-and-what-could-happen-maduro-gone</t>
+          <t>https://www.researchgate.net/publication/261537223_The_Chinese-Venezuelan_Oil_Agreements_Material_and_Nonmaterial_Goals</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VEN-0120</t>
+          <t>VEN-0101</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>120101</v>
+        <v>101101</v>
       </c>
       <c r="C51" t="n">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7.4616708036399, -63.3128864565516</t>
+          <t>10.8744001388549, -71.8973999023437</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6371,31 +5774,31 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>VE-F</t>
+          <t>VE-V</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2012</v>
+        <v>1997</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>China Railway Tenth Group</t>
+          <t>China National Petroleum Corporation</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -6409,25 +5812,22 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Adquisicion De Participación En Pdvsa Para Crear Petrolera Sino-Venezolana I Y Ii</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Acquisition Of Stake In Pdvsa To Create Petrolera Sino-Venezolana I And Ii</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>BOLÍVAR</t>
-        </is>
-      </c>
-      <c r="R51" t="n">
-        <v>550</v>
+          <t>ZULIA</t>
+        </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Adquisición</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6441,47 +5841,39 @@
         </is>
       </c>
       <c r="BA51" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB51" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC51" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>https://www.cnpc.com.cn/en/America/CNPC_Latin_America.shtml</t>
+        </is>
+      </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>https://fundacionandresbello.org/wp-content/uploads/2024/07/pera-perfil-empresa-cnpc-venezuela.pdf</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF51" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
-        <is>
-          <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
+          <t>https://www.researchgate.net/publication/261537223_The_Chinese-Venezuelan_Oil_Agreements_Material_and_Nonmaterial_Goals</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VEN-0120</t>
+          <t>VEN-0101</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>120101</v>
+        <v>101101</v>
       </c>
       <c r="C52" t="n">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7.45565054830144, -63.3002919163913</t>
+          <t>9.00345993041992, -64.5117034912109</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6494,31 +5886,31 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>VE-F</t>
+          <t>VE-B</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2012</v>
+        <v>1997</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>China Railway Tenth Group</t>
+          <t>China National Petroleum Corporation</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -6532,25 +5924,22 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Adquisicion De Participación En Pdvsa Para Crear Petrolera Sino-Venezolana I Y Ii</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Acquisition Of Stake In Pdvsa To Create Petrolera Sino-Venezolana I And Ii</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>BOLÍVAR</t>
-        </is>
-      </c>
-      <c r="R52" t="n">
-        <v>550</v>
+          <t>ANZOÁTEGUI</t>
+        </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Adquisición</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6564,47 +5953,39 @@
         </is>
       </c>
       <c r="BA52" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB52" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC52" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>https://www.cnpc.com.cn/en/America/CNPC_Latin_America.shtml</t>
+        </is>
+      </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>https://fundacionandresbello.org/wp-content/uploads/2024/07/pera-perfil-empresa-cnpc-venezuela.pdf</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF52" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG52" t="inlineStr">
-        <is>
-          <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
+          <t>https://www.researchgate.net/publication/261537223_The_Chinese-Venezuelan_Oil_Agreements_Material_and_Nonmaterial_Goals</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VEN-0120</t>
+          <t>VEN-0103</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>120101</v>
+        <v>103101</v>
       </c>
       <c r="C53" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7.53263033551216, -63.2252922949616</t>
+          <t>8.729480, -63.100300</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6617,31 +5998,31 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>VE-F</t>
+          <t>VE-B</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>China Railway Tenth Group</t>
+          <t>China National Petroleum Corporation</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -6655,25 +6036,25 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Adquisicion De Participación En Pdvsa Para Crear Petrolera Sinovensa</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Acquisition Of Stake In Pdvsa To Create Petrolera Sinvensa</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>BOLÍVAR</t>
+          <t>ANZOÁTEGUI</t>
         </is>
       </c>
       <c r="R53" t="n">
-        <v>550</v>
+        <v>4015</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Adquisición</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -6687,29 +6068,21 @@
         </is>
       </c>
       <c r="BA53" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB53" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC53" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/energy/en/news-research/latest-news/crude-oil/091520-venezuela-sinovensa-petromonagas-and-petropiar-jvs-restart-production-pdvsa</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/38053/</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF53" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr">
-        <is>
-          <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
+          <t>https://www.scmp.com/economy/global-economy/article/3338807/what-assets-does-china-have-venezuela-and-what-could-happen-maduro-gone</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6100,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.54695382765539, -63.2185393812773</t>
+          <t>7.4616708036399, -63.3128864565516</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6740,7 +6113,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -6778,12 +6151,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -6812,25 +6185,17 @@
       <c r="BA54" t="n">
         <v>3</v>
       </c>
-      <c r="BB54" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC54" t="n">
-        <v>0</v>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF54" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG54" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -6850,7 +6215,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7.55246040782578, -63.2062981855727</t>
+          <t>7.45565054830144, -63.3002919163913</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6863,7 +6228,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -6901,12 +6266,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -6935,25 +6300,17 @@
       <c r="BA55" t="n">
         <v>3</v>
       </c>
-      <c r="BB55" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC55" t="n">
-        <v>0</v>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF55" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -6973,7 +6330,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.55502715028421, -63.2027569584128</t>
+          <t>7.53263033551216, -63.2252922949616</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6986,7 +6343,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -7024,12 +6381,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -7058,25 +6415,17 @@
       <c r="BA56" t="n">
         <v>3</v>
       </c>
-      <c r="BB56" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC56" t="n">
-        <v>0</v>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF56" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7096,7 +6445,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7.59397482018983, -63.1866464424716</t>
+          <t>7.54695382765539, -63.2185393812773</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7109,7 +6458,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -7147,12 +6496,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -7181,25 +6530,17 @@
       <c r="BA57" t="n">
         <v>3</v>
       </c>
-      <c r="BB57" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC57" t="n">
-        <v>0</v>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF57" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG57" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7219,7 +6560,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.61422665542898, -63.1703161956502</t>
+          <t>7.55246040782578, -63.2062981855727</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7232,7 +6573,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -7270,12 +6611,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -7304,25 +6645,17 @@
       <c r="BA58" t="n">
         <v>3</v>
       </c>
-      <c r="BB58" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC58" t="n">
-        <v>0</v>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF58" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG58" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7342,7 +6675,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7.62517135341522, -63.1668302237649</t>
+          <t>7.55502715028421, -63.2027569584128</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7355,7 +6688,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -7393,12 +6726,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -7427,25 +6760,17 @@
       <c r="BA59" t="n">
         <v>3</v>
       </c>
-      <c r="BB59" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC59" t="n">
-        <v>0</v>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF59" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG59" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7465,7 +6790,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7.63858165249449, -63.1552955925217</t>
+          <t>7.59397482018983, -63.1866464424716</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7478,7 +6803,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -7516,12 +6841,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -7550,25 +6875,17 @@
       <c r="BA60" t="n">
         <v>3</v>
       </c>
-      <c r="BB60" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC60" t="n">
-        <v>0</v>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF60" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7588,7 +6905,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7.64374281249071, -63.1546803320695</t>
+          <t>7.61422665542898, -63.1703161956502</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7601,7 +6918,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -7639,12 +6956,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -7673,25 +6990,17 @@
       <c r="BA61" t="n">
         <v>3</v>
       </c>
-      <c r="BB61" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC61" t="n">
-        <v>0</v>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF61" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG61" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7711,7 +7020,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>7.64589034580271, -63.1521816874805</t>
+          <t>7.62517135341522, -63.1668302237649</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7724,7 +7033,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -7762,12 +7071,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -7796,25 +7105,17 @@
       <c r="BA62" t="n">
         <v>3</v>
       </c>
-      <c r="BB62" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC62" t="n">
-        <v>0</v>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF62" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7834,7 +7135,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7.65416838843969, -63.1528437189886</t>
+          <t>7.63858165249449, -63.1552955925217</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7847,7 +7148,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -7885,12 +7186,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -7919,25 +7220,17 @@
       <c r="BA63" t="n">
         <v>3</v>
       </c>
-      <c r="BB63" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC63" t="n">
-        <v>0</v>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF63" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG63" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7957,7 +7250,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7.6696266935032, -63.1482489981885</t>
+          <t>7.64374281249071, -63.1546803320695</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7970,7 +7263,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -8008,12 +7301,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -8042,25 +7335,17 @@
       <c r="BA64" t="n">
         <v>3</v>
       </c>
-      <c r="BB64" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC64" t="n">
-        <v>0</v>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF64" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG64" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8080,7 +7365,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7.67499827618559, -63.1515293727838</t>
+          <t>7.64589034580271, -63.1521816874805</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -8093,7 +7378,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -8131,12 +7416,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -8165,25 +7450,17 @@
       <c r="BA65" t="n">
         <v>3</v>
       </c>
-      <c r="BB65" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC65" t="n">
-        <v>0</v>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF65" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8203,7 +7480,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7.68211153536846, -63.1547319412955</t>
+          <t>7.65416838843969, -63.1528437189886</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -8216,7 +7493,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -8254,12 +7531,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -8288,25 +7565,17 @@
       <c r="BA66" t="n">
         <v>3</v>
       </c>
-      <c r="BB66" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC66" t="n">
-        <v>0</v>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF66" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG66" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8326,7 +7595,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7.70748825049613, -63.1630938304615</t>
+          <t>7.6696266935032, -63.1482489981885</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8339,7 +7608,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -8377,12 +7646,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -8411,25 +7680,17 @@
       <c r="BA67" t="n">
         <v>3</v>
       </c>
-      <c r="BB67" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC67" t="n">
-        <v>0</v>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF67" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG67" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8449,7 +7710,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7.77772207635082, -63.1462337922043</t>
+          <t>7.67499827618559, -63.1515293727838</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8462,7 +7723,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -8500,12 +7761,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -8534,25 +7795,17 @@
       <c r="BA68" t="n">
         <v>3</v>
       </c>
-      <c r="BB68" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC68" t="n">
-        <v>0</v>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF68" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG68" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8572,7 +7825,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7.80007806403915, -63.1166259568096</t>
+          <t>7.68211153536846, -63.1547319412955</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8585,7 +7838,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -8623,12 +7876,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -8657,25 +7910,17 @@
       <c r="BA69" t="n">
         <v>3</v>
       </c>
-      <c r="BB69" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC69" t="n">
-        <v>0</v>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF69" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG69" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8695,7 +7940,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7.85996681517291, -63.0976281306481</t>
+          <t>7.70748825049613, -63.1630938304615</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8708,7 +7953,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -8746,12 +7991,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -8780,25 +8025,17 @@
       <c r="BA70" t="n">
         <v>3</v>
       </c>
-      <c r="BB70" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC70" t="n">
-        <v>0</v>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF70" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG70" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8818,7 +8055,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>7.87326060595224, -63.0862087474813</t>
+          <t>7.77772207635082, -63.1462337922043</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8831,7 +8068,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -8869,12 +8106,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -8903,25 +8140,17 @@
       <c r="BA71" t="n">
         <v>3</v>
       </c>
-      <c r="BB71" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC71" t="n">
-        <v>0</v>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF71" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG71" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8941,7 +8170,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7.87334631642841, -63.0747323335012</t>
+          <t>7.80007806403915, -63.1166259568096</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8954,7 +8183,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -8992,12 +8221,12 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -9026,25 +8255,17 @@
       <c r="BA72" t="n">
         <v>3</v>
       </c>
-      <c r="BB72" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC72" t="n">
-        <v>0</v>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF72" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG72" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9064,7 +8285,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7.91706931561339, -63.0446359141799</t>
+          <t>7.85996681517291, -63.0976281306481</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -9077,7 +8298,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -9115,12 +8336,12 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -9149,25 +8370,17 @@
       <c r="BA73" t="n">
         <v>3</v>
       </c>
-      <c r="BB73" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC73" t="n">
-        <v>0</v>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF73" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG73" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9187,7 +8400,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>7.92068186844131, -63.0440654387432</t>
+          <t>7.87326060595224, -63.0862087474813</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -9200,7 +8413,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -9238,12 +8451,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -9272,25 +8485,17 @@
       <c r="BA74" t="n">
         <v>3</v>
       </c>
-      <c r="BB74" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC74" t="n">
-        <v>0</v>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF74" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG74" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9310,7 +8515,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7.95566394424672, -63.0601531519004</t>
+          <t>7.87334631642841, -63.0747323335012</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -9323,7 +8528,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -9361,12 +8566,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -9395,25 +8600,17 @@
       <c r="BA75" t="n">
         <v>3</v>
       </c>
-      <c r="BB75" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC75" t="n">
-        <v>0</v>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF75" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG75" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9433,7 +8630,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>8.01189239141298, -63.0588736598421</t>
+          <t>7.91706931561339, -63.0446359141799</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -9446,7 +8643,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -9484,12 +8681,12 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -9518,25 +8715,17 @@
       <c r="BA76" t="n">
         <v>3</v>
       </c>
-      <c r="BB76" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC76" t="n">
-        <v>0</v>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF76" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG76" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9556,7 +8745,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>8.02895116423727, -63.0353020336721</t>
+          <t>7.92068186844131, -63.0440654387432</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -9569,7 +8758,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -9607,12 +8796,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -9641,25 +8830,17 @@
       <c r="BA77" t="n">
         <v>3</v>
       </c>
-      <c r="BB77" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC77" t="n">
-        <v>0</v>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF77" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG77" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9679,7 +8860,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8.07220056041887, -63.0298753649327</t>
+          <t>7.95566394424672, -63.0601531519004</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9692,7 +8873,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -9730,12 +8911,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -9764,25 +8945,17 @@
       <c r="BA78" t="n">
         <v>3</v>
       </c>
-      <c r="BB78" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC78" t="n">
-        <v>0</v>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF78" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG78" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9802,7 +8975,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8.09903128567286, -62.9465271821478</t>
+          <t>8.01189239141298, -63.0588736598421</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9815,7 +8988,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -9853,12 +9026,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -9887,25 +9060,17 @@
       <c r="BA79" t="n">
         <v>3</v>
       </c>
-      <c r="BB79" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC79" t="n">
-        <v>0</v>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
-        <is>
-          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
-        </is>
-      </c>
-      <c r="BF79" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/37541/</t>
-        </is>
-      </c>
-      <c r="BG79" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9925,7 +9090,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>8.10787402817201, -62.9334841224794</t>
+          <t>8.02895116423727, -63.0353020336721</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9938,7 +9103,7 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="1" t="inlineStr">
         <is>
           <t>862</t>
         </is>
@@ -9976,12 +9141,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Construcción en expansión del ferrocarril de la Ferrominera Orinoco</t>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Construction on Ferrominera Orinoco railway expansion</t>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -10010,25 +9175,362 @@
       <c r="BA80" t="n">
         <v>3</v>
       </c>
-      <c r="BB80" t="inlineStr">
-        <is>
-          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
-        </is>
-      </c>
-      <c r="BC80" t="n">
-        <v>0</v>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
+          <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>VEN-0120</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>120101</v>
+      </c>
+      <c r="C81" t="n">
+        <v>120</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>8.07220056041887, -63.0298753649327</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>VE-F</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>China Railway Tenth Group</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>550</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BA81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BF80" t="inlineStr">
+      <c r="BD81" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BG80" t="inlineStr">
+      <c r="BE81" t="inlineStr">
+        <is>
+          <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>VEN-0120</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>120101</v>
+      </c>
+      <c r="C82" t="n">
+        <v>120</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>8.09903128567286, -62.9465271821478</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>VE-F</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>China Railway Tenth Group</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>550</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BA82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
+      </c>
+      <c r="BE82" t="inlineStr">
+        <is>
+          <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>VEN-0120</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>120101</v>
+      </c>
+      <c r="C83" t="n">
+        <v>120</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>8.10787402817201, -62.9334841224794</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>VE-F</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>China Railway Tenth Group</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Construcción En Expansión Del Ferrocarril De La Ferrominera Orinoco</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Construction On Ferrominera Orinoco Railway Expansion</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="R83" t="n">
+        <v>550</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BA83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
+        </is>
+      </c>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/37541/</t>
+        </is>
+      </c>
+      <c r="BE83" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>

--- a/data/sources/countries/venezuela.xlsx
+++ b/data/sources/countries/venezuela.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE83"/>
+  <dimension ref="A1:BG83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,20 +684,30 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
@@ -731,10 +740,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G2" t="n">
+        <v>862</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -785,6 +792,9 @@
       <c r="R2" t="n">
         <v>1000</v>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -800,6 +810,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Sistema SIMA-VEN911 de CEIEC. Confirmado por el Departamento del Tesoro de EEUU, que sanciono a la empresa en 2020, el informe de Transparencia Venezuela, Global Voices, TalCual e Infobae. ATENCION AL MONTO: el anuncio de 2013 fue de USD 1.200M, no 1.000, para 40 centros de mando en 16 localidades y 30.000 camaras, y Transparencia Venezuela estima sobreprecio de hasta USD 350M. Es monto anunciado, no ejecutado verificado.</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -828,10 +877,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G3" t="n">
+        <v>862</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -880,8 +927,11 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -897,6 +947,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>MONTO CORREGIDO de 4 a 161. Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -925,10 +1014,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G4" t="n">
+        <v>862</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -977,8 +1064,11 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -994,6 +1084,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1022,10 +1151,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G5" t="n">
+        <v>862</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1074,8 +1201,11 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1091,6 +1221,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1119,10 +1288,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G6" t="n">
+        <v>862</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1171,8 +1338,11 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1188,6 +1358,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1216,10 +1425,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G7" t="n">
+        <v>862</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1268,8 +1475,11 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1285,6 +1495,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1313,10 +1562,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G8" t="n">
+        <v>862</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1365,8 +1612,11 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1382,6 +1632,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1410,10 +1699,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G9" t="n">
+        <v>862</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1462,8 +1749,11 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1479,6 +1769,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1507,10 +1836,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G10" t="n">
+        <v>862</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1559,8 +1886,11 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1576,6 +1906,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1604,10 +1973,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G11" t="n">
+        <v>862</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1656,8 +2023,11 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1673,6 +2043,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1701,10 +2110,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G12" t="n">
+        <v>862</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1753,8 +2160,11 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1770,6 +2180,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1798,10 +2247,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G13" t="n">
+        <v>862</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1850,8 +2297,11 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1867,6 +2317,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1895,10 +2384,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G14" t="n">
+        <v>862</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1947,8 +2434,11 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1964,6 +2454,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1992,10 +2521,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G15" t="n">
+        <v>862</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2044,8 +2571,11 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2061,6 +2591,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2089,10 +2658,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G16" t="n">
+        <v>862</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2141,8 +2708,11 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2158,6 +2728,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2186,10 +2795,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G17" t="n">
+        <v>862</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2238,8 +2845,11 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2255,6 +2865,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2283,10 +2932,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G18" t="n">
+        <v>862</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2335,8 +2982,11 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2352,6 +3002,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2380,10 +3069,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G19" t="n">
+        <v>862</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2432,8 +3119,11 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2449,6 +3139,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2477,10 +3206,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G20" t="n">
+        <v>862</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2529,8 +3256,11 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2546,6 +3276,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2574,10 +3343,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G21" t="n">
+        <v>862</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2626,8 +3393,11 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2643,6 +3413,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2671,10 +3480,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G22" t="n">
+        <v>862</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2723,8 +3530,11 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2740,6 +3550,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2768,10 +3617,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G23" t="n">
+        <v>862</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2820,8 +3667,11 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2837,6 +3687,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2865,10 +3754,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G24" t="n">
+        <v>862</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2917,8 +3804,11 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2934,6 +3824,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2962,10 +3891,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G25" t="n">
+        <v>862</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3014,8 +3941,11 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3031,6 +3961,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3059,10 +4028,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G26" t="n">
+        <v>862</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3111,8 +4078,11 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3128,6 +4098,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3156,10 +4165,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G27" t="n">
+        <v>862</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3208,8 +4215,11 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3225,6 +4235,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3253,10 +4302,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G28" t="n">
+        <v>862</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3305,8 +4352,11 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3322,6 +4372,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3350,10 +4439,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G29" t="n">
+        <v>862</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3402,8 +4489,11 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3419,6 +4509,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3447,10 +4576,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G30" t="n">
+        <v>862</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3499,8 +4626,11 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3516,6 +4646,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3544,10 +4713,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G31" t="n">
+        <v>862</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3596,8 +4763,11 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3613,6 +4783,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3641,10 +4850,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G32" t="n">
+        <v>862</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3693,8 +4900,11 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3710,6 +4920,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3738,10 +4987,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G33" t="n">
+        <v>862</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -3790,8 +5037,11 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3807,6 +5057,45 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>Ferrominera firmo con CCCC el 5 de septiembre de 2011 el contrato de dragado de mantenimiento y profundizacion del canal del Orinoco entre las millas 0 y 42, por USD 161M, con las dragas autopropulsadas Xin Hai Ma y Hang Jun 5001 para retirar unos cinco millones de metros cubicos en 116 dias. Confirmado por MundoMaritimo, la investigacion conjunta de Dialogo Chino y El Clip, Runrun y El Diario de Guayana. Esta entrada nunca habia sido auditada.</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3835,10 +5124,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G34" t="n">
+        <v>862</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -3889,6 +5176,9 @@
       <c r="R34" t="n">
         <v>550</v>
       </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3904,20 +5194,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
         <v>4</v>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>Confirmado: Wison Engineering (junto a Hyundai) ganó contrato EPC para mejora de la refinería Puerto La Cruz (PDVSA), con contrato total de \~USD 2.993B anunciado en 2012. La porción de Wison fue \~USD 927M. El monto registrado USD 550M podría ser un contrato parcial o la fase de preparación del sitio. Wison.com, PR Newswire y AidData confirman el proyecto. Discrepancia en monto: la entrada (USD 550M) podría corresponder a un subcontrato específico.</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr">
         <is>
           <t>https://www.wison.com/en/read_page/819</t>
         </is>
       </c>
-      <c r="BD34" t="inlineStr">
+      <c r="BF34" t="inlineStr">
         <is>
           <t>https://www.prnewswire.com/news-releases/wison-wins-puerto-la-cruz-oil-refinery-in-venezuela-160517955.html</t>
         </is>
       </c>
-      <c r="BE34" t="inlineStr">
+      <c r="BG34" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/58367/</t>
         </is>
@@ -3950,10 +5275,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G35" t="n">
+        <v>862</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -4004,6 +5327,9 @@
       <c r="R35" t="n">
         <v>1190</v>
       </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4019,20 +5345,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
         <v>4</v>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>Confirmado: CITIC Construction fue contratada para el proyecto habitacional en Ciudad Tiuna (Fuerte Tiuna, Caracas), construyendo 13.034 apartamentos en 116 edificios. El sitio oficial de CITIC Construction, People's Daily y la ceremonia de entrega presidencial confirman el proyecto. El monto USD 1.190M no aparece explícitamente en las fuentes encontradas pero es coherente con la magnitud del proyecto (13.034 unidades).</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr">
         <is>
           <t>https://www.construction.citic/en/global/project/lad/2660</t>
         </is>
       </c>
-      <c r="BD35" t="inlineStr">
+      <c r="BF35" t="inlineStr">
         <is>
           <t>https://en.people.cn/n/2015/0505/c90883-8887435.html</t>
         </is>
       </c>
-      <c r="BE35" t="inlineStr">
+      <c r="BG35" t="inlineStr">
         <is>
           <t>https://www.construction.citic/en/news/latest/2432</t>
         </is>
@@ -4065,10 +5426,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G36" t="n">
+        <v>862</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -4119,6 +5478,9 @@
       <c r="R36" t="n">
         <v>10</v>
       </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -4134,20 +5496,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
         <v>4</v>
       </c>
-      <c r="BC36" t="inlineStr">
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>Confirmado: ZTE y CORPIVENSA crearon Vtelca (empresa mixta, ZTE 15.7%, CORPIVENSA 84.3%) en Punto Fijo, Falcón, inaugurada en febrero 2009. AidData registra el proyecto con USD 19.5M. Wikipedia en español y Orinoco Tribune confirman la empresa y su historia. El monto USD 10M en la base de datos es inferior a los USD 19.5M de AidData; posible diferencia entre aportación de ZTE y costo total.</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37442/</t>
         </is>
       </c>
-      <c r="BD36" t="inlineStr">
+      <c r="BF36" t="inlineStr">
         <is>
           <t>https://es.wikipedia.org/wiki/Vtelca</t>
         </is>
       </c>
-      <c r="BE36" t="inlineStr">
+      <c r="BG36" t="inlineStr">
         <is>
           <t>https://orinocotribune.com/president-maduro-celebrates-the-first-10-years-of-vtelca/</t>
         </is>
@@ -4180,10 +5577,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G37" t="n">
+        <v>862</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4234,6 +5629,9 @@
       <c r="R37" t="n">
         <v>960</v>
       </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4249,20 +5647,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
         <v>3</v>
       </c>
-      <c r="BC37" t="inlineStr">
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>Confirmado que CAMC Engineering (filial de Sinomach/China Machinery) fue el contratista de la Termoeléctrica Don Luis Zambrano en El Vigía, Mérida (470-570 MW). El inversor registrado es 'China National Machinery Industry Corporation' (Sinomach), que coincide con CAMC. El monto USD 960M es inferior al costo final del proyecto (\~USD 1.045B-1.7B según fuentes, con sobrecostos y corrupción documentada). Score 3 por confirmación del contratista y proyecto con discrepancias de monto y corrupción documentada.</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr">
         <is>
           <t>https://fundacionandresbello.org/wp-content/uploads/2024/05/perfil-proyecto-termoelectrica-donluiszambrano-pera.pdf</t>
         </is>
       </c>
-      <c r="BD37" t="inlineStr">
+      <c r="BF37" t="inlineStr">
         <is>
           <t>http://www.camce.com.cn/sp/enNews/enGN/201505/t20150504_59848.html</t>
         </is>
       </c>
-      <c r="BE37" t="inlineStr">
+      <c r="BG37" t="inlineStr">
         <is>
           <t>https://www.power-technology.com/data-insights/power-plant-profile-don-luis-zambrano-power-plant-venezuela/</t>
         </is>
@@ -4295,10 +5728,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G38" t="n">
+        <v>862</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -4349,6 +5780,9 @@
       <c r="R38" t="n">
         <v>520</v>
       </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4364,20 +5798,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
         <v>5</v>
       </c>
-      <c r="BC38" t="inlineStr">
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>Totalmente confirmado: Bolipuertos y CHEC (China Harbor Engineering, filial de CCCC) firmaron acuerdo en 2011 para construir terminal de contenedores en Puerto Cabello por USD 520M. Offshore Energy, WorldCargo News y Ship Technology confirman todos los detalles (inversor, monto, ubicación). El inversor 'CCCC' en la base de datos es correcto (CHEC es filial).</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr">
         <is>
           <t>https://www.offshore-energy.biz/venezuela-bolipuertos-chec-agree-to-build-container-terminal-in-puerto-cabello-port/</t>
         </is>
       </c>
-      <c r="BD38" t="inlineStr">
+      <c r="BF38" t="inlineStr">
         <is>
           <t>https://www.worldcargonews.com/ports-terminals/2011/10/bolipuertoschec-sign-puerto-cabello-agreement/</t>
         </is>
       </c>
-      <c r="BE38" t="inlineStr">
+      <c r="BG38" t="inlineStr">
         <is>
           <t>https://www.ship-technology.com/news/newsbolipuertos-and-chec-to-build-new-terminal-at-puerto-cabello-port-venezuela/</t>
         </is>
@@ -4410,10 +5879,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G39" t="n">
+        <v>862</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -4464,6 +5931,9 @@
       <c r="R39" t="n">
         <v>1310</v>
       </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4479,20 +5949,59 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
         <v>1</v>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>Se confirma que Corpoelec adjudicó contrato a Dongfang Electric en octubre 2014 para modernización de 6 turbinas-generadores de la central Simón Bolívar (Guri). Sin embargo, las fuentes principales de la modernización histórica mencionan a ABB y Andritz Hydro como contratistas principales. Allison señala que según CAF y BID, la Corporación Eléctrica Nacional S.A. (venezolana) es la encargada de la construcción. El monto de USD 1,310M parece muy elevado y no se pudo confirmar. El contrato de Dongfang parece ser para suministro de equipos, no construcción completa.</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
         <is>
           <t>https://www.power-technology.com/projects/gurihydroelectric/</t>
         </is>
       </c>
-      <c r="BD39" t="inlineStr">
+      <c r="BF39" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Guri_Dam</t>
         </is>
       </c>
-      <c r="BE39" t="inlineStr">
+      <c r="BG39" t="inlineStr">
         <is>
           <t>https://www.hydroreview.com/world-regions/venezuela-further-extends-engineering-call-to-upgrade-10-300-mw-simon-bolivar-hydro-project/</t>
         </is>
@@ -4525,10 +6034,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G40" t="n">
+        <v>862</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4576,6 +6083,10 @@
           <t>ANZOÁTEGUI</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -4591,20 +6102,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
         <v>4</v>
       </c>
-      <c r="BC40" t="inlineStr">
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>Confirmado: CNPC y PDVSA firmaron en 2004-2007 el JV Petrozumano para explotar el Campo Zumano (Anzoátegui), CNPC con 40%. AidData, Fundación Andrés Bello y Venezuelanalysis confirman el JV. El monto '200\*' (con asterisco, indicando estimación) es coherente con la participación. El año 2007 corresponde a la formalización del JV mediante decreto presidencial.</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/38053/</t>
         </is>
       </c>
-      <c r="BD40" t="inlineStr">
+      <c r="BF40" t="inlineStr">
         <is>
           <t>https://fundacionandresbello.org/wp-content/uploads/2024/07/pera-perfil-empresa-cnpc-venezuela.pdf</t>
         </is>
       </c>
-      <c r="BE40" t="inlineStr">
+      <c r="BG40" t="inlineStr">
         <is>
           <t>https://venezuelanalysis.com/news/15307/</t>
         </is>
@@ -4637,10 +6183,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G41" t="n">
+        <v>862</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4691,6 +6235,9 @@
       <c r="R41" t="n">
         <v>900</v>
       </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -4706,20 +6253,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
         <v>4</v>
       </c>
-      <c r="BC41" t="inlineStr">
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>Confirmado: CNPC y PDVSA formaron Petrourica (PDVSA 60%, CNPC 40%), JV creado formalmente en diciembre 2011. AidData, Venezuelanalysis y Enerdata confirman el JV. El monto USD 900M y el año 2010 (registro de la negociación/acuerdo previo a la formalización) son coherentes con la inversión china en el bloque Orinoco. Score 4 por múltiples fuentes con leve discrepancia en la fecha exacta de formalización.</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/38053/</t>
         </is>
       </c>
-      <c r="BD41" t="inlineStr">
+      <c r="BF41" t="inlineStr">
         <is>
           <t>https://venezuelanalysis.com/news/15307/</t>
         </is>
       </c>
-      <c r="BE41" t="inlineStr">
+      <c r="BG41" t="inlineStr">
         <is>
           <t>https://www.enerdata.net/publications/daily-energy-news/pdvsa-secures-new-us22bn-financing-cnpc-raise-oil-output.html</t>
         </is>
@@ -4752,10 +6334,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G42" t="n">
+        <v>862</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4767,7 +6347,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>China Great Wall Industry Corporation</t>
+          <t>Sinomach</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4806,6 +6386,9 @@
       <c r="R42" t="n">
         <v>140</v>
       </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4821,19 +6404,59 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
         <v>1</v>
       </c>
-      <c r="BC42" t="inlineStr">
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>La rehabilitacion del sistema de riego del Rio Guarico la ejecuto Sinomach, no China Great Wall Industry Corporation, que se especializa en satelites y lanzamientos.</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
         <is>
           <t>https://inventariandochina.wordpress.com/2015/10/22/un-contrato-entre-venezuela-y-la-great-wall-industry-corporation/</t>
         </is>
       </c>
-      <c r="BD42" t="inlineStr">
+      <c r="BF42" t="inlineStr">
         <is>
           <t>https://fundacionandresbello.org/wp-content/uploads/2024/05/perfil-proyecto-riegorioguarico-pera.pdf</t>
         </is>
       </c>
+      <c r="BG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4862,10 +6485,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G43" t="n">
+        <v>862</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4916,6 +6537,9 @@
       <c r="R43" t="n">
         <v>132</v>
       </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -4931,19 +6555,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
         <v>3</v>
       </c>
-      <c r="BC43" t="inlineStr">
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>Confirmado por LatinFinance y AidData. Venezuela cedió 9.9% adicional de Petrolera Sinovensa a CNPC en 2018, elevando participación de CNPC Venezuela BV a 49.9%. Base registra $132M. Contexto: proyecto petrolero Orinoco, financiamiento CDB $4B.</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr">
         <is>
           <t>https://latinfinance.com/daily-brief/2018/09/18/venezuela-cedes-sinovensa-stake-to-cnpc/</t>
         </is>
       </c>
-      <c r="BD43" t="inlineStr">
+      <c r="BF43" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/38053/</t>
         </is>
       </c>
+      <c r="BG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4972,10 +6632,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G44" t="n">
+        <v>862</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5026,6 +6684,9 @@
       <c r="R44" t="n">
         <v>604</v>
       </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5041,20 +6702,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
         <v>4</v>
       </c>
-      <c r="BC44" t="inlineStr">
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>Confirmado: Sinohydro construyó la planta termoeléctrica La Cabrera (José Félix Ribas, 320 MW) en la costa norte del Lago Valencia. BNamericas, Power Technology y Dialogue Earth confirman el proyecto y el contratista. El monto USD 604M coincide con las fuentes. Nota: la planta fue comisionada en abril 2014, no 2010; el año 2010 posiblemente refleja inicio del contrato o construcción.</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/electricpower/venezuela-starts-up-320mw-thermo-plant</t>
         </is>
       </c>
-      <c r="BD44" t="inlineStr">
+      <c r="BF44" t="inlineStr">
         <is>
           <t>https://www.power-technology.com/data-insights/power-plant-profile-jose-felix-ribas-la-cabrera-power-plant-venezuela/</t>
         </is>
       </c>
-      <c r="BE44" t="inlineStr">
+      <c r="BG44" t="inlineStr">
         <is>
           <t>https://dialogue.earth/en/energy/32585-chinese-investment-in-venezuelas-grid-fails-to-prevent-blackouts/</t>
         </is>
@@ -5087,10 +6783,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G45" t="n">
+        <v>862</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5141,6 +6835,9 @@
       <c r="R45" t="n">
         <v>500</v>
       </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5156,20 +6853,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
         <v>3</v>
       </c>
-      <c r="BC45" t="inlineStr">
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>Confirmado que Chalieco (filial de Aluminum Corp. of China/Chalco) firmó contrato de USD 403M con CVG-Alcasa para modernización de fundiciones en Ciudad Guayana en 2011 (no 2014). El inversor 'Aluminum Corporation of China' coincide con el contratista. S\&amp;P Global Platts, Light Metal Age y Aluminium Insider confirman el proyecto. Discrepancias: año (2011 vs 2014) y monto (USD 403M vs USD 500M). Score 3 por confirmación del proyecto con discrepancias.</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr">
         <is>
           <t>https://www.spglobal.com/commodityinsights/es/market-insights/latest-news/metals/110411-venezuelas-cvg-alcasa-signs-403-mil-modernization-deal-with-chalieco</t>
         </is>
       </c>
-      <c r="BD45" t="inlineStr">
+      <c r="BF45" t="inlineStr">
         <is>
           <t>https://www.lightmetalage.com/news/industry-news/smelting/the-decline-of-venezuelas-aluminum-industry/</t>
         </is>
       </c>
-      <c r="BE45" t="inlineStr">
+      <c r="BG45" t="inlineStr">
         <is>
           <t>https://aluminiuminsider.com/can-venezuelas-primary-aluminium-industry-survive/</t>
         </is>
@@ -5202,10 +6934,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G46" t="n">
+        <v>862</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5256,6 +6986,9 @@
       <c r="R46" t="n">
         <v>112</v>
       </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5271,20 +7004,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
         <v>4</v>
       </c>
-      <c r="BC46" t="inlineStr">
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>Confirmado: AidData registra explícitamente un contrato para expansión del Puerto de Palúa otorgado a una corporación china, y BNamericas confirma la expansión de Ferrominera. The Siasat Daily describe el proyecto con China Railway 10th Group. El monto USD 112M y la fecha 2011 están corroborados (el contrato fue dado por CVG Ferrominera el 5 de septiembre 2011). El muelle fue inaugurado en 2017, cinco años tarde.</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37940/</t>
         </is>
       </c>
-      <c r="BD46" t="inlineStr">
+      <c r="BF46" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BE46" t="inlineStr">
+      <c r="BG46" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -5317,10 +7085,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G47" t="n">
+        <v>862</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5371,6 +7137,9 @@
       <c r="R47" t="n">
         <v>278</v>
       </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -5386,20 +7155,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="n">
         <v>5</v>
       </c>
-      <c r="BC47" t="inlineStr">
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>Totalmente confirmado: Yutong y el gobierno venezolano inauguraron la planta ensambladora en San Felipe, Yaracuy, el 2 de diciembre de 2015, con inversión de USD 278M. TeleSUR, ChinaBuses.org y el Ministerio de Transporte venezolano confirman todos los detalles (inversor, monto, ubicación, fecha, estructura del JV con 85% gobierno / 15% Yutong).</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr">
         <is>
           <t>https://www.telesurenglish.net/news/Maduro-Opens-Venzeulas-First-Yutong-Bus-Plant-20151203-0006.html</t>
         </is>
       </c>
-      <c r="BD47" t="inlineStr">
+      <c r="BF47" t="inlineStr">
         <is>
           <t>https://www.chinabuses.org/news/2015/0721/article_9024.html</t>
         </is>
       </c>
-      <c r="BE47" t="inlineStr">
+      <c r="BG47" t="inlineStr">
         <is>
           <t>https://www.mppt.gob.ve/2016/planta-de-autobuses-yutong-venezuela-ha-ensamblado-100-autobuses-desde-su-inauguracion-en-diciembre/</t>
         </is>
@@ -5432,10 +7236,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G48" t="n">
+        <v>862</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5486,6 +7288,9 @@
       <c r="R48" t="n">
         <v>1650</v>
       </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -5501,20 +7306,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
       <c r="BA48" t="n">
         <v>4</v>
       </c>
-      <c r="BC48" t="inlineStr">
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>Confirmado: en noviembre 2016, PDVSA y CNPC firmaron acuerdo de USD 2.200M para proyectos de productividad en Petrozumano y Petrourica. Venezuelanalysis, Enerdata y AidData confirman el acuerdo. El monto USD 1.650M en la base de datos difiere del total de USD 2.200M; podría ser la porción asignada a Petrozumano+Petrourica específicamente (USD 225M + USD 500M = USD 725M; o incluyendo otros fondos). Fecha 2016 es correcta.</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr">
         <is>
           <t>https://venezuelanalysis.com/news/12792/</t>
         </is>
       </c>
-      <c r="BD48" t="inlineStr">
+      <c r="BF48" t="inlineStr">
         <is>
           <t>https://www.enerdata.net/publications/daily-energy-news/pdvsa-secures-new-us22bn-financing-cnpc-raise-oil-output.html</t>
         </is>
       </c>
-      <c r="BE48" t="inlineStr">
+      <c r="BG48" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/58413/</t>
         </is>
@@ -5547,10 +7387,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G49" t="n">
+        <v>862</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5601,6 +7439,9 @@
       <c r="R49" t="n">
         <v>1650</v>
       </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -5616,20 +7457,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
         <v>4</v>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>Confirmado: en noviembre 2016, PDVSA y CNPC firmaron acuerdo de USD 2.200M para proyectos de productividad en Petrozumano y Petrourica. Venezuelanalysis, Enerdata y AidData confirman el acuerdo. El monto USD 1.650M en la base de datos difiere del total de USD 2.200M; podría ser la porción asignada a Petrozumano+Petrourica específicamente (USD 225M + USD 500M = USD 725M; o incluyendo otros fondos). Fecha 2016 es correcta.</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr">
         <is>
           <t>https://venezuelanalysis.com/news/12792/</t>
         </is>
       </c>
-      <c r="BD49" t="inlineStr">
+      <c r="BF49" t="inlineStr">
         <is>
           <t>https://www.enerdata.net/publications/daily-energy-news/pdvsa-secures-new-us22bn-financing-cnpc-raise-oil-output.html</t>
         </is>
       </c>
-      <c r="BE49" t="inlineStr">
+      <c r="BG49" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/58413/</t>
         </is>
@@ -5662,10 +7538,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G50" t="n">
+        <v>862</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -5713,6 +7587,10 @@
           <t>BOLÍVAR</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -5728,20 +7606,51 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
         <v>4</v>
       </c>
-      <c r="BC50" t="inlineStr">
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr">
         <is>
           <t>https://www.cnpc.com.cn/en/America/CNPC_Latin_America.shtml</t>
         </is>
       </c>
-      <c r="BD50" t="inlineStr">
+      <c r="BF50" t="inlineStr">
         <is>
           <t>https://fundacionandresbello.org/wp-content/uploads/2024/07/pera-perfil-empresa-cnpc-venezuela.pdf</t>
         </is>
       </c>
-      <c r="BE50" t="inlineStr">
+      <c r="BG50" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/261537223_The_Chinese-Venezuelan_Oil_Agreements_Material_and_Nonmaterial_Goals</t>
         </is>
@@ -5774,10 +7683,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G51" t="n">
+        <v>862</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -5825,6 +7732,10 @@
           <t>ZULIA</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -5840,20 +7751,51 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
         <v>4</v>
       </c>
-      <c r="BC51" t="inlineStr">
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr">
         <is>
           <t>https://www.cnpc.com.cn/en/America/CNPC_Latin_America.shtml</t>
         </is>
       </c>
-      <c r="BD51" t="inlineStr">
+      <c r="BF51" t="inlineStr">
         <is>
           <t>https://fundacionandresbello.org/wp-content/uploads/2024/07/pera-perfil-empresa-cnpc-venezuela.pdf</t>
         </is>
       </c>
-      <c r="BE51" t="inlineStr">
+      <c r="BG51" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/261537223_The_Chinese-Venezuelan_Oil_Agreements_Material_and_Nonmaterial_Goals</t>
         </is>
@@ -5886,10 +7828,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G52" t="n">
+        <v>862</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -5937,6 +7877,10 @@
           <t>ANZOÁTEGUI</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -5952,20 +7896,51 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
         <v>4</v>
       </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr">
         <is>
           <t>https://www.cnpc.com.cn/en/America/CNPC_Latin_America.shtml</t>
         </is>
       </c>
-      <c r="BD52" t="inlineStr">
+      <c r="BF52" t="inlineStr">
         <is>
           <t>https://fundacionandresbello.org/wp-content/uploads/2024/07/pera-perfil-empresa-cnpc-venezuela.pdf</t>
         </is>
       </c>
-      <c r="BE52" t="inlineStr">
+      <c r="BG52" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/261537223_The_Chinese-Venezuelan_Oil_Agreements_Material_and_Nonmaterial_Goals</t>
         </is>
@@ -5998,10 +7973,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G53" t="n">
+        <v>862</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6052,6 +8025,9 @@
       <c r="R53" t="n">
         <v>4015</v>
       </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -6067,20 +8043,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
         <v>4</v>
       </c>
-      <c r="BC53" t="inlineStr">
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>Confirmado: Sinovensa (PetroSinovensa) fue constituida como JV entre CVP y CNPC Venezuela B.V. en febrero 2008 (Gaceta Oficial N°38.860), con 60% CVP / 40% CNPC. S\&amp;P Global, AidData y SCMP confirman la existencia y detalles del JV. El monto '2000\*' (estimado) para múltiples campos no es verificable directamente; el JV es bien documentado.</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr">
         <is>
           <t>https://www.spglobal.com/energy/en/news-research/latest-news/crude-oil/091520-venezuela-sinovensa-petromonagas-and-petropiar-jvs-restart-production-pdvsa</t>
         </is>
       </c>
-      <c r="BD53" t="inlineStr">
+      <c r="BF53" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/38053/</t>
         </is>
       </c>
-      <c r="BE53" t="inlineStr">
+      <c r="BG53" t="inlineStr">
         <is>
           <t>https://www.scmp.com/economy/global-economy/article/3338807/what-assets-does-china-have-venezuela-and-what-could-happen-maduro-gone</t>
         </is>
@@ -6113,10 +8124,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G54" t="n">
+        <v>862</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -6167,6 +8176,9 @@
       <c r="R54" t="n">
         <v>550</v>
       </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6182,20 +8194,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
         <v>3</v>
       </c>
-      <c r="BC54" t="inlineStr">
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr"/>
+      <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD54" t="inlineStr">
+      <c r="BF54" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE54" t="inlineStr">
+      <c r="BG54" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -6228,10 +8275,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G55" t="n">
+        <v>862</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -6282,6 +8327,9 @@
       <c r="R55" t="n">
         <v>550</v>
       </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6297,20 +8345,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
         <v>3</v>
       </c>
-      <c r="BC55" t="inlineStr">
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD55" t="inlineStr">
+      <c r="BF55" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE55" t="inlineStr">
+      <c r="BG55" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -6343,10 +8426,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G56" t="n">
+        <v>862</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -6397,6 +8478,9 @@
       <c r="R56" t="n">
         <v>550</v>
       </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6412,20 +8496,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
         <v>3</v>
       </c>
-      <c r="BC56" t="inlineStr">
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD56" t="inlineStr">
+      <c r="BF56" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE56" t="inlineStr">
+      <c r="BG56" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -6458,10 +8577,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G57" t="n">
+        <v>862</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -6512,6 +8629,9 @@
       <c r="R57" t="n">
         <v>550</v>
       </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6527,20 +8647,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="inlineStr"/>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
         <v>3</v>
       </c>
-      <c r="BC57" t="inlineStr">
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr"/>
+      <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD57" t="inlineStr">
+      <c r="BF57" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE57" t="inlineStr">
+      <c r="BG57" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -6573,10 +8728,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G58" t="n">
+        <v>862</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -6627,6 +8780,9 @@
       <c r="R58" t="n">
         <v>550</v>
       </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6642,20 +8798,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="inlineStr"/>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr"/>
+      <c r="AX58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
         <v>3</v>
       </c>
-      <c r="BC58" t="inlineStr">
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr"/>
+      <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD58" t="inlineStr">
+      <c r="BF58" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE58" t="inlineStr">
+      <c r="BG58" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -6688,10 +8879,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G59" t="n">
+        <v>862</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -6742,6 +8931,9 @@
       <c r="R59" t="n">
         <v>550</v>
       </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6757,20 +8949,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="inlineStr"/>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
         <v>3</v>
       </c>
-      <c r="BC59" t="inlineStr">
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr"/>
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD59" t="inlineStr">
+      <c r="BF59" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE59" t="inlineStr">
+      <c r="BG59" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -6803,10 +9030,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G60" t="n">
+        <v>862</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -6857,6 +9082,9 @@
       <c r="R60" t="n">
         <v>550</v>
       </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6872,20 +9100,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
         <v>3</v>
       </c>
-      <c r="BC60" t="inlineStr">
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr"/>
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD60" t="inlineStr">
+      <c r="BF60" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE60" t="inlineStr">
+      <c r="BG60" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -6918,10 +9181,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G61" t="n">
+        <v>862</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -6972,6 +9233,9 @@
       <c r="R61" t="n">
         <v>550</v>
       </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6987,20 +9251,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
         <v>3</v>
       </c>
-      <c r="BC61" t="inlineStr">
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr"/>
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD61" t="inlineStr">
+      <c r="BF61" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE61" t="inlineStr">
+      <c r="BG61" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7033,10 +9332,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G62" t="n">
+        <v>862</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -7087,6 +9384,9 @@
       <c r="R62" t="n">
         <v>550</v>
       </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7102,20 +9402,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr"/>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
         <v>3</v>
       </c>
-      <c r="BC62" t="inlineStr">
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr"/>
+      <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD62" t="inlineStr">
+      <c r="BF62" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE62" t="inlineStr">
+      <c r="BG62" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7148,10 +9483,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G63" t="n">
+        <v>862</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -7202,6 +9535,9 @@
       <c r="R63" t="n">
         <v>550</v>
       </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7217,20 +9553,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="inlineStr"/>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr"/>
+      <c r="AV63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr"/>
+      <c r="AX63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
         <v>3</v>
       </c>
-      <c r="BC63" t="inlineStr">
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr"/>
+      <c r="BD63" t="inlineStr"/>
+      <c r="BE63" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD63" t="inlineStr">
+      <c r="BF63" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE63" t="inlineStr">
+      <c r="BG63" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7263,10 +9634,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G64" t="n">
+        <v>862</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -7317,6 +9686,9 @@
       <c r="R64" t="n">
         <v>550</v>
       </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7332,20 +9704,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr"/>
+      <c r="AX64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
         <v>3</v>
       </c>
-      <c r="BC64" t="inlineStr">
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr"/>
+      <c r="BD64" t="inlineStr"/>
+      <c r="BE64" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD64" t="inlineStr">
+      <c r="BF64" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE64" t="inlineStr">
+      <c r="BG64" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7378,10 +9785,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G65" t="n">
+        <v>862</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -7432,6 +9837,9 @@
       <c r="R65" t="n">
         <v>550</v>
       </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7447,20 +9855,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
         <v>3</v>
       </c>
-      <c r="BC65" t="inlineStr">
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr"/>
+      <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD65" t="inlineStr">
+      <c r="BF65" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE65" t="inlineStr">
+      <c r="BG65" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7493,10 +9936,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G66" t="n">
+        <v>862</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -7547,6 +9988,9 @@
       <c r="R66" t="n">
         <v>550</v>
       </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7562,20 +10006,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="inlineStr"/>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AU66" t="inlineStr"/>
+      <c r="AV66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr"/>
+      <c r="AX66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr"/>
       <c r="BA66" t="n">
         <v>3</v>
       </c>
-      <c r="BC66" t="inlineStr">
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr"/>
+      <c r="BD66" t="inlineStr"/>
+      <c r="BE66" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD66" t="inlineStr">
+      <c r="BF66" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE66" t="inlineStr">
+      <c r="BG66" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7608,10 +10087,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G67" t="n">
+        <v>862</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -7662,6 +10139,9 @@
       <c r="R67" t="n">
         <v>550</v>
       </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7677,20 +10157,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="inlineStr"/>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AU67" t="inlineStr"/>
+      <c r="AV67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr"/>
+      <c r="AX67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr"/>
       <c r="BA67" t="n">
         <v>3</v>
       </c>
-      <c r="BC67" t="inlineStr">
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr"/>
+      <c r="BD67" t="inlineStr"/>
+      <c r="BE67" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD67" t="inlineStr">
+      <c r="BF67" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE67" t="inlineStr">
+      <c r="BG67" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7723,10 +10238,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G68" t="n">
+        <v>862</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -7777,6 +10290,9 @@
       <c r="R68" t="n">
         <v>550</v>
       </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7792,20 +10308,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr"/>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="inlineStr"/>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr"/>
+      <c r="AV68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr"/>
+      <c r="AX68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
         <v>3</v>
       </c>
-      <c r="BC68" t="inlineStr">
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr"/>
+      <c r="BD68" t="inlineStr"/>
+      <c r="BE68" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD68" t="inlineStr">
+      <c r="BF68" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE68" t="inlineStr">
+      <c r="BG68" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7838,10 +10389,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G69" t="n">
+        <v>862</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -7892,6 +10441,9 @@
       <c r="R69" t="n">
         <v>550</v>
       </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7907,20 +10459,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr"/>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
         <v>3</v>
       </c>
-      <c r="BC69" t="inlineStr">
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr"/>
+      <c r="BD69" t="inlineStr"/>
+      <c r="BE69" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD69" t="inlineStr">
+      <c r="BF69" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE69" t="inlineStr">
+      <c r="BG69" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -7953,10 +10540,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G70" t="n">
+        <v>862</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -8007,6 +10592,9 @@
       <c r="R70" t="n">
         <v>550</v>
       </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8022,20 +10610,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="inlineStr"/>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr"/>
+      <c r="AX70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
         <v>3</v>
       </c>
-      <c r="BC70" t="inlineStr">
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr"/>
+      <c r="BD70" t="inlineStr"/>
+      <c r="BE70" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD70" t="inlineStr">
+      <c r="BF70" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE70" t="inlineStr">
+      <c r="BG70" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8068,10 +10691,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G71" t="n">
+        <v>862</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -8122,6 +10743,9 @@
       <c r="R71" t="n">
         <v>550</v>
       </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8137,20 +10761,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr"/>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
         <v>3</v>
       </c>
-      <c r="BC71" t="inlineStr">
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr"/>
+      <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD71" t="inlineStr">
+      <c r="BF71" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE71" t="inlineStr">
+      <c r="BG71" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8183,10 +10842,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G72" t="n">
+        <v>862</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -8237,6 +10894,9 @@
       <c r="R72" t="n">
         <v>550</v>
       </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8252,20 +10912,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
         <v>3</v>
       </c>
-      <c r="BC72" t="inlineStr">
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr"/>
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD72" t="inlineStr">
+      <c r="BF72" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE72" t="inlineStr">
+      <c r="BG72" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8298,10 +10993,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G73" t="n">
+        <v>862</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -8352,6 +11045,9 @@
       <c r="R73" t="n">
         <v>550</v>
       </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8367,20 +11063,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
         <v>3</v>
       </c>
-      <c r="BC73" t="inlineStr">
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD73" t="inlineStr">
+      <c r="BF73" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE73" t="inlineStr">
+      <c r="BG73" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8413,10 +11144,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G74" t="n">
+        <v>862</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -8467,6 +11196,9 @@
       <c r="R74" t="n">
         <v>550</v>
       </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8482,20 +11214,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr"/>
+      <c r="AQ74" t="inlineStr"/>
+      <c r="AR74" t="inlineStr"/>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AU74" t="inlineStr"/>
+      <c r="AV74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr"/>
+      <c r="AX74" t="inlineStr"/>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr"/>
       <c r="BA74" t="n">
         <v>3</v>
       </c>
-      <c r="BC74" t="inlineStr">
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr"/>
+      <c r="BD74" t="inlineStr"/>
+      <c r="BE74" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD74" t="inlineStr">
+      <c r="BF74" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE74" t="inlineStr">
+      <c r="BG74" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8528,10 +11295,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G75" t="n">
+        <v>862</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -8582,6 +11347,9 @@
       <c r="R75" t="n">
         <v>550</v>
       </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8597,20 +11365,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="inlineStr"/>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AU75" t="inlineStr"/>
+      <c r="AV75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr"/>
+      <c r="AX75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
         <v>3</v>
       </c>
-      <c r="BC75" t="inlineStr">
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr"/>
+      <c r="BD75" t="inlineStr"/>
+      <c r="BE75" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD75" t="inlineStr">
+      <c r="BF75" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE75" t="inlineStr">
+      <c r="BG75" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8643,10 +11446,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G76" t="n">
+        <v>862</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -8697,6 +11498,9 @@
       <c r="R76" t="n">
         <v>550</v>
       </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8712,20 +11516,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="inlineStr"/>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AU76" t="inlineStr"/>
+      <c r="AV76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr"/>
+      <c r="AX76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
         <v>3</v>
       </c>
-      <c r="BC76" t="inlineStr">
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="inlineStr"/>
+      <c r="BE76" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD76" t="inlineStr">
+      <c r="BF76" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE76" t="inlineStr">
+      <c r="BG76" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8758,10 +11597,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G77" t="n">
+        <v>862</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -8812,6 +11649,9 @@
       <c r="R77" t="n">
         <v>550</v>
       </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8827,20 +11667,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="inlineStr"/>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AU77" t="inlineStr"/>
+      <c r="AV77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr"/>
+      <c r="AX77" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
         <v>3</v>
       </c>
-      <c r="BC77" t="inlineStr">
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr"/>
+      <c r="BD77" t="inlineStr"/>
+      <c r="BE77" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD77" t="inlineStr">
+      <c r="BF77" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE77" t="inlineStr">
+      <c r="BG77" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8873,10 +11748,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G78" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G78" t="n">
+        <v>862</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -8927,6 +11800,9 @@
       <c r="R78" t="n">
         <v>550</v>
       </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8942,20 +11818,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="inlineStr"/>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AU78" t="inlineStr"/>
+      <c r="AV78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr"/>
+      <c r="AX78" t="inlineStr"/>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
         <v>3</v>
       </c>
-      <c r="BC78" t="inlineStr">
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr"/>
+      <c r="BD78" t="inlineStr"/>
+      <c r="BE78" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD78" t="inlineStr">
+      <c r="BF78" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE78" t="inlineStr">
+      <c r="BG78" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -8988,10 +11899,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G79" t="n">
+        <v>862</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -9042,6 +11951,9 @@
       <c r="R79" t="n">
         <v>550</v>
       </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -9057,20 +11969,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="inlineStr"/>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AU79" t="inlineStr"/>
+      <c r="AV79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr"/>
+      <c r="AX79" t="inlineStr"/>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr"/>
       <c r="BA79" t="n">
         <v>3</v>
       </c>
-      <c r="BC79" t="inlineStr">
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr"/>
+      <c r="BD79" t="inlineStr"/>
+      <c r="BE79" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD79" t="inlineStr">
+      <c r="BF79" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE79" t="inlineStr">
+      <c r="BG79" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9103,10 +12050,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G80" t="n">
+        <v>862</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -9157,6 +12102,9 @@
       <c r="R80" t="n">
         <v>550</v>
       </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -9172,20 +12120,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr"/>
       <c r="BA80" t="n">
         <v>3</v>
       </c>
-      <c r="BC80" t="inlineStr">
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="inlineStr"/>
+      <c r="BE80" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD80" t="inlineStr">
+      <c r="BF80" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE80" t="inlineStr">
+      <c r="BG80" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9218,10 +12201,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G81" t="n">
+        <v>862</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -9272,6 +12253,9 @@
       <c r="R81" t="n">
         <v>550</v>
       </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -9287,20 +12271,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AU81" t="inlineStr"/>
+      <c r="AV81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr"/>
+      <c r="AX81" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr"/>
       <c r="BA81" t="n">
         <v>3</v>
       </c>
-      <c r="BC81" t="inlineStr">
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD81" t="inlineStr">
+      <c r="BF81" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE81" t="inlineStr">
+      <c r="BG81" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9333,10 +12352,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G82" t="n">
+        <v>862</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -9387,6 +12404,9 @@
       <c r="R82" t="n">
         <v>550</v>
       </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -9402,20 +12422,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr"/>
+      <c r="AR82" t="inlineStr"/>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AU82" t="inlineStr"/>
+      <c r="AV82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr"/>
+      <c r="AX82" t="inlineStr"/>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
         <v>3</v>
       </c>
-      <c r="BC82" t="inlineStr">
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD82" t="inlineStr">
+      <c r="BF82" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE82" t="inlineStr">
+      <c r="BG82" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
@@ -9448,10 +12503,8 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
+      <c r="G83" t="n">
+        <v>862</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -9502,6 +12555,9 @@
       <c r="R83" t="n">
         <v>550</v>
       </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -9517,20 +12573,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="inlineStr"/>
+      <c r="AP83" t="inlineStr"/>
+      <c r="AQ83" t="inlineStr"/>
+      <c r="AR83" t="inlineStr"/>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AU83" t="inlineStr"/>
+      <c r="AV83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr"/>
+      <c r="AX83" t="inlineStr"/>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="n">
         <v>3</v>
       </c>
-      <c r="BC83" t="inlineStr">
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>Confirmado que China Railway Tenth Group participó en la expansión ferroviaria de Ferrominera Orinoco. BNamericas, AidData (CDB presta USD 1.000M para proyectos CVG minería) y The Siasat Daily mencionan el proyecto ferroviario. El monto USD 550M (vs. USD 473M en algunas fuentes para el contrato de Palúa/ferroviario) y año 2012 son aproximadamente correctos. El proyecto tuvo importantes problemas de ejecución.</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr"/>
+      <c r="BD83" t="inlineStr"/>
+      <c r="BE83" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/ferrominera-orinoco-resumes-railway-expansion-project</t>
         </is>
       </c>
-      <c r="BD83" t="inlineStr">
+      <c r="BF83" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/37541/</t>
         </is>
       </c>
-      <c r="BE83" t="inlineStr">
+      <c r="BG83" t="inlineStr">
         <is>
           <t>https://archive.siasat.com/news/chinas-greed-for-natural-resources-drives-venezuela-into-the-ground-2093459/</t>
         </is>
